--- a/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
+++ b/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FF8D84-32BC-4122-8198-DC91355F61F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97579D5-7CA7-47F7-9035-2E694CDB0719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
+    <sheet name="NBCForm" sheetId="3" r:id="rId2"/>
+    <sheet name="Users" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
   <si>
     <t>Client</t>
   </si>
@@ -176,6 +177,330 @@
   </si>
   <si>
     <t>Dental</t>
+  </si>
+  <si>
+    <t>ErrorList</t>
+  </si>
+  <si>
+    <t>FinancialOpinion</t>
+  </si>
+  <si>
+    <t>TranOverview</t>
+  </si>
+  <si>
+    <t>CurrentStatus</t>
+  </si>
+  <si>
+    <t>CompDesc</t>
+  </si>
+  <si>
+    <t>CrossBorder</t>
+  </si>
+  <si>
+    <t>AsiaAngle</t>
+  </si>
+  <si>
+    <t>OwnershipStr</t>
+  </si>
+  <si>
+    <t>TotalDebt</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>EstVal</t>
+  </si>
+  <si>
+    <t>ValExp</t>
+  </si>
+  <si>
+    <t>RiskFactors</t>
+  </si>
+  <si>
+    <t>ExtFee</t>
+  </si>
+  <si>
+    <t>FeeStru</t>
+  </si>
+  <si>
+    <t>LockUps</t>
+  </si>
+  <si>
+    <t>ReferralFee</t>
+  </si>
+  <si>
+    <t>Pitch</t>
+  </si>
+  <si>
+    <t>HLComp</t>
+  </si>
+  <si>
+    <t>ExistingRel</t>
+  </si>
+  <si>
+    <t>TASAssist</t>
+  </si>
+  <si>
+    <t>OutsideCouncil</t>
+  </si>
+  <si>
+    <t>CapMkt</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Fairness</t>
+  </si>
+  <si>
+    <t>ResList</t>
+  </si>
+  <si>
+    <t>CCStatus1</t>
+  </si>
+  <si>
+    <t>CCStatus2</t>
+  </si>
+  <si>
+    <t>CCStatus3</t>
+  </si>
+  <si>
+    <t>CCStatus4</t>
+  </si>
+  <si>
+    <t>Tabs</t>
+  </si>
+  <si>
+    <t>ValTotalDebt</t>
+  </si>
+  <si>
+    <t>ValEstValuation</t>
+  </si>
+  <si>
+    <t>ValCurrentStatus</t>
+  </si>
+  <si>
+    <t>ValValuationExp</t>
+  </si>
+  <si>
+    <t>ValCompDesc</t>
+  </si>
+  <si>
+    <t>ValRealEstate</t>
+  </si>
+  <si>
+    <t>ValOwnership</t>
+  </si>
+  <si>
+    <t>ValAsiaAngle</t>
+  </si>
+  <si>
+    <t>ValRiskFact</t>
+  </si>
+  <si>
+    <t>ValInternational</t>
+  </si>
+  <si>
+    <t>ValCapMkt</t>
+  </si>
+  <si>
+    <t>ValExistingFin</t>
+  </si>
+  <si>
+    <t>ValFinSub</t>
+  </si>
+  <si>
+    <t>ValNoFin</t>
+  </si>
+  <si>
+    <t>ValRetainer</t>
+  </si>
+  <si>
+    <t>ValRetainerFee</t>
+  </si>
+  <si>
+    <t>ValProgFee</t>
+  </si>
+  <si>
+    <t>ValTxnFee</t>
+  </si>
+  <si>
+    <t>valWillThere</t>
+  </si>
+  <si>
+    <t>ValHLComp</t>
+  </si>
+  <si>
+    <t>ValLockups</t>
+  </si>
+  <si>
+    <t>ValExisting</t>
+  </si>
+  <si>
+    <t>ValExistingRepeat</t>
+  </si>
+  <si>
+    <t>ValTAS</t>
+  </si>
+  <si>
+    <t>ValOutside</t>
+  </si>
+  <si>
+    <t>ValFairness</t>
+  </si>
+  <si>
+    <t>ValA</t>
+  </si>
+  <si>
+    <t>ValB</t>
+  </si>
+  <si>
+    <t>ValC</t>
+  </si>
+  <si>
+    <t>ValD</t>
+  </si>
+  <si>
+    <t>valGroup</t>
+  </si>
+  <si>
+    <t>valUpdRetainer</t>
+  </si>
+  <si>
+    <t>valUpdRetainerCred</t>
+  </si>
+  <si>
+    <t>FromAmt</t>
+  </si>
+  <si>
+    <t>ToAmt</t>
+  </si>
+  <si>
+    <t>UpdEstValue</t>
+  </si>
+  <si>
+    <t>Opportunity Overview: Transaction Overview</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Pitched</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No. Established client relationship.</t>
+  </si>
+  <si>
+    <t>OVERVIEW AND FINANCIALS, FEES, PITCH, FINANCING CHECKLIST, FAIRNESS CHECKLIST, ADMINISTRATIVE</t>
+  </si>
+  <si>
+    <t>Total Debt (MM)/r/nOpportunity Overview: Total Debt(MM)</t>
+  </si>
+  <si>
+    <t>Opportunity Overview: Valuation Expectations</t>
+  </si>
+  <si>
+    <t>Current Status/r/nOpportunity Overview: Current Status</t>
+  </si>
+  <si>
+    <t>Opportunity Overview: Company Description</t>
+  </si>
+  <si>
+    <t>Real Estate Angle/r/nOpportunity Overview: Real Estate Angle</t>
+  </si>
+  <si>
+    <t>Opportunity Overview: Ownership Structure &amp; Capital Structure</t>
+  </si>
+  <si>
+    <t>Asia Angle/r/nOpportunity Overview: Asia Angle</t>
+  </si>
+  <si>
+    <t>Opportunity Overview: Risk Factors</t>
+  </si>
+  <si>
+    <t>International Angle?/r/nOpportunity Overview: Cross-border Angle</t>
+  </si>
+  <si>
+    <t>Capital Markets Consulted/r/nFinancing Checklist: Has the Capital Markets Group been consulted regarding financing or capital structure?</t>
+  </si>
+  <si>
+    <t>Financing Checklist: Please summarize the existing financial arrangements.</t>
+  </si>
+  <si>
+    <t>Financials Subject to Audit/r/nFinancials: Have the financials been subject to an audit?</t>
+  </si>
+  <si>
+    <t>Insufficient Financials/r/nFinancials: Add min 2 Historical or current and future Financial records when submitting the NBC form</t>
+  </si>
+  <si>
+    <t>Retainer/r/nFees: "Retainer info required, enter 0 if none</t>
+  </si>
+  <si>
+    <t>Retainer Fee Creditable ?/r/nThe value can't be null for 'Retainer Fee Creditable'</t>
+  </si>
+  <si>
+    <t>Progress Fee Creditable ?/r/nThe value can't be null for 'Progress Fee Creditable ?'</t>
+  </si>
+  <si>
+    <t>Select a transaction type value.</t>
+  </si>
+  <si>
+    <t>Will There Be a Pitch?/r/nPre-Pitch: Will there be a pitch?</t>
+  </si>
+  <si>
+    <t>Pre-Pitch: Please identify Houlihan Lokey competition.</t>
+  </si>
+  <si>
+    <t>Lockups on Future M&amp;A or Financing Work/r/nPre-Pitch: Lockups on Future M&amp;A or Financing Work</t>
+  </si>
+  <si>
+    <t>Existing Relationships/r/nPre-Pitch: Have you checked Salesforce for existing relationships?</t>
+  </si>
+  <si>
+    <t>Existing or Repeat Client?/r/nPre-Pitch: Existing or Repeat Client?</t>
+  </si>
+  <si>
+    <t>TAS/Bridge Assistance Benefit?/r/nPre-Pitch: Would the Opportunity benefit from TAS Assistance?</t>
+  </si>
+  <si>
+    <t>Pre-Pitch: If known, identify the name(s) of the client’s outside counsel and/or other advisors (If any)</t>
+  </si>
+  <si>
+    <t>Fairness Opinion Provided/r/nFairness Checklist: Is there a potential Fairness Opinion component to this assignment?</t>
+  </si>
+  <si>
+    <t>A/r/nPublic Sensitivity: Please answer the Public M&amp;A question.</t>
+  </si>
+  <si>
+    <t>B/r/nPublic Sensitivity: Please answer the Public M&amp;A question.</t>
+  </si>
+  <si>
+    <t>C/r/nPublic Sensitivity: Please answer the Public M&amp;A question.</t>
+  </si>
+  <si>
+    <t>D/r/nPublic Sensitivity: Please answer the Public M&amp;A question.</t>
+  </si>
+  <si>
+    <t>Group Head Approval/r/nOpportunity Overview: Please confirm that a group head has approved prior to submitting to the committee.</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>15.00</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>80.00</t>
   </si>
 </sst>
 </file>
@@ -246,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -258,6 +583,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,6 +1085,428 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3BC8A9-AAA5-46B4-A523-F7B0C33218AB}">
+  <dimension ref="A1:BP2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:68" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BE1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="BG1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="BH1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BI1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="BJ1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP1" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:68" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL2" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM2" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN2" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP2" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR2" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT2" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU2" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV2" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX2" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY2" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA2" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB2" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="BC2" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="BD2" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="BE2" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="BF2" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="BG2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="BH2" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="BI2" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="BJ2" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="BK2" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BO2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BP2" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
+++ b/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97579D5-7CA7-47F7-9035-2E694CDB0719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC5E7D-9F69-4683-A091-522B7BE5B123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="160">
   <si>
     <t>Client</t>
   </si>
@@ -501,6 +501,12 @@
   </si>
   <si>
     <t>80.00</t>
+  </si>
+  <si>
+    <t>Buyside</t>
+  </si>
+  <si>
+    <t>Sellside</t>
   </si>
 </sst>
 </file>
@@ -881,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -1078,6 +1084,178 @@
         <v>34</v>
       </c>
     </row>
+    <row r="3" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" t="s">
+        <v>31</v>
+      </c>
+      <c r="X4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
+++ b/TestData/VerifyTheFunctionalityOfTheRemovalOfTheMinimumFeeFromECMJobTypeForFlatFee_Part2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC5E7D-9F69-4683-A091-522B7BE5B123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843BC2F4-7FC4-418F-AAF1-B01259F6F79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>Brian Miller</t>
   </si>
   <si>
-    <t>Equity Capital Markets</t>
-  </si>
-  <si>
     <t>HC - Healthcare</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   </si>
   <si>
     <t>Sellside</t>
+  </si>
+  <si>
+    <t>Equity Placements</t>
   </si>
 </sst>
 </file>
@@ -1006,13 +1006,13 @@
         <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" t="s">
         <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -1092,13 +1092,13 @@
         <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
         <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1178,13 +1178,13 @@
         <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
         <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -1269,225 +1269,225 @@
   <sheetData>
     <row r="1" spans="1:68" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="S1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="W1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AM1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AN1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="AO1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AP1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AR1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AS1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AT1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AU1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AV1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AW1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="AX1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AX1" s="7" t="s">
+      <c r="AY1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AY1" s="7" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AZ1" s="7" t="s">
+      <c r="BA1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="BA1" s="7" t="s">
+      <c r="BB1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="BC1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="BC1" s="7" t="s">
+      <c r="BD1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="BD1" s="7" t="s">
+      <c r="BE1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BF1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BG1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="BG1" s="7" t="s">
+      <c r="BH1" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BI1" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BK1" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BL1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BM1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BN1" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BO1" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BP1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="BP1" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:68" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>119</v>
-      </c>
       <c r="E2" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>7</v>
@@ -1496,22 +1496,22 @@
         <v>7</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>34</v>
@@ -1526,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S2" s="11" t="s">
         <v>7</v>
@@ -1568,115 +1568,115 @@
         <v>7</v>
       </c>
       <c r="AF2" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AJ2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK2" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="AJ2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AL2" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AM2" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AN2" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AO2" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AP2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="AR2" s="12" t="s">
+      <c r="AS2" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="AS2" s="12" t="s">
+      <c r="AT2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AU2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AV2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AW2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AX2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AX2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="AY2" s="12" t="s">
+      <c r="AZ2" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="BA2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BB2" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="BB2" s="12" t="s">
+      <c r="BC2" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="BC2" s="12" t="s">
+      <c r="BD2" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="BD2" s="12" t="s">
+      <c r="BE2" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="BE2" s="12" t="s">
+      <c r="BF2" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="BF2" s="12" t="s">
+      <c r="BG2" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="BH2" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="BI2" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="BK2" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="BL2" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="BL2" s="3" t="s">
+      <c r="BM2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="BM2" s="3" t="s">
+      <c r="BN2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BO2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="BO2" s="3" t="s">
+      <c r="BP2" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="BP2" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
